--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_5.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_individual_h_5.xlsx
@@ -658,7 +658,7 @@
         <v>0.03125777900766041</v>
       </c>
       <c r="C2" t="n">
-        <v>31063860</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>31063860</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>22646322</v>
+        <v>4200450</v>
       </c>
       <c r="L2" t="n">
-        <v>13679200</v>
+        <v>2331449</v>
       </c>
       <c r="M2" t="n">
-        <v>3590844</v>
+        <v>569968</v>
       </c>
       <c r="N2" t="n">
-        <v>214925</v>
+        <v>27386</v>
       </c>
       <c r="O2" t="n">
-        <v>2124268</v>
+        <v>354195</v>
       </c>
       <c r="P2" t="n">
-        <v>846145</v>
+        <v>148358</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999690055847168</v>
+        <v>0.9999269247055054</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9234642386436462</v>
+        <v>0.8563995957374573</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8380125164985657</v>
+        <v>0.7134827375411987</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7827841639518738</v>
+        <v>0.6232850551605225</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6293520927429199</v>
+        <v>0.4036256372928619</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8334237933158875</v>
+        <v>0.6948569416999817</v>
       </c>
       <c r="W2" t="n">
-        <v>0.878700852394104</v>
+        <v>0.7700988054275513</v>
       </c>
       <c r="X2" t="n">
-        <v>31063860</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>31063860</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>21956039</v>
+        <v>4098451</v>
       </c>
       <c r="AG2" t="n">
-        <v>12547940</v>
+        <v>2160035</v>
       </c>
       <c r="AH2" t="n">
-        <v>3229049</v>
+        <v>523313</v>
       </c>
       <c r="AI2" t="n">
-        <v>196806</v>
+        <v>26078</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1941860</v>
+        <v>326935</v>
       </c>
       <c r="AK2" t="n">
-        <v>795961</v>
+        <v>139695</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.889315664768219</v>
+        <v>0.8300260305404663</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.7832459211349487</v>
+        <v>0.6741499304771423</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6973374485969543</v>
+        <v>0.565066933631897</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4453732967376709</v>
+        <v>0.2950734198093414</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7644305229187012</v>
+        <v>0.6435044407844543</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.8237075805664062</v>
+        <v>0.7228233218193054</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.008287393333615061</v>
       </c>
       <c r="C3" t="n">
-        <v>190</v>
+        <v>112</v>
       </c>
       <c r="D3" t="n">
-        <v>22646322</v>
+        <v>4200450</v>
       </c>
       <c r="E3" t="n">
-        <v>1852426</v>
+        <v>664697</v>
       </c>
       <c r="F3" t="n">
-        <v>60794</v>
+        <v>24633</v>
       </c>
       <c r="G3" t="n">
-        <v>12268</v>
+        <v>4249</v>
       </c>
       <c r="H3" t="n">
-        <v>1722</v>
+        <v>1084</v>
       </c>
       <c r="I3" t="n">
-        <v>274</v>
+        <v>102</v>
       </c>
       <c r="J3" t="n">
-        <v>49287178</v>
+        <v>9857174</v>
       </c>
       <c r="K3" t="n">
-        <v>53901101</v>
+        <v>10470745</v>
       </c>
       <c r="L3" t="n">
-        <v>61594314</v>
+        <v>11894941</v>
       </c>
       <c r="M3" t="n">
-        <v>74709337</v>
+        <v>14794405</v>
       </c>
       <c r="N3" t="n">
-        <v>79782335</v>
+        <v>15941176</v>
       </c>
       <c r="O3" t="n">
-        <v>77382689</v>
+        <v>15405420</v>
       </c>
       <c r="P3" t="n">
-        <v>79268610</v>
+        <v>15832717</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9215563535690308</v>
+        <v>0.8580529689788818</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8489277958869934</v>
+        <v>0.7197594046592712</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7728502750396729</v>
+        <v>0.6118786334991455</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4850616455078125</v>
+        <v>0.3085398972034454</v>
       </c>
       <c r="V3" t="n">
-        <v>0.834770143032074</v>
+        <v>0.6952674984931946</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8753963708877563</v>
+        <v>0.7671322226524353</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>21956039</v>
+        <v>4098451</v>
       </c>
       <c r="Z3" t="n">
-        <v>2441958</v>
+        <v>740530</v>
       </c>
       <c r="AA3" t="n">
-        <v>113298</v>
+        <v>38881</v>
       </c>
       <c r="AB3" t="n">
-        <v>58886</v>
+        <v>15351</v>
       </c>
       <c r="AC3" t="n">
-        <v>3367</v>
+        <v>1917</v>
       </c>
       <c r="AD3" t="n">
-        <v>448</v>
+        <v>197</v>
       </c>
       <c r="AE3" t="n">
-        <v>49288140</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>53045353</v>
+        <v>10335786</v>
       </c>
       <c r="AG3" t="n">
-        <v>60766003</v>
+        <v>11787142</v>
       </c>
       <c r="AH3" t="n">
-        <v>74304274</v>
+        <v>14736100</v>
       </c>
       <c r="AI3" t="n">
-        <v>79663828</v>
+        <v>15919340</v>
       </c>
       <c r="AJ3" t="n">
-        <v>77208856</v>
+        <v>15379844</v>
       </c>
       <c r="AK3" t="n">
-        <v>79215061</v>
+        <v>15823439</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8934663534164429</v>
+        <v>0.8372169733047485</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7787221074104309</v>
+        <v>0.6668409109115601</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.6949818730354309</v>
+        <v>0.5617930293083191</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4441691040992737</v>
+        <v>0.2938035130500793</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.7630895972251892</v>
+        <v>0.6417574882507324</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.8234775066375732</v>
+        <v>0.7223374247550964</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.07326137193158536</v>
       </c>
       <c r="C4" t="n">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
-        <v>1778297</v>
+        <v>669109</v>
       </c>
       <c r="E4" t="n">
-        <v>13679200</v>
+        <v>2331449</v>
       </c>
       <c r="F4" t="n">
-        <v>591666</v>
+        <v>207929</v>
       </c>
       <c r="G4" t="n">
-        <v>19337</v>
+        <v>7588</v>
       </c>
       <c r="H4" t="n">
-        <v>41258</v>
+        <v>20964</v>
       </c>
       <c r="I4" t="n">
-        <v>3670</v>
+        <v>2126</v>
       </c>
       <c r="J4" t="n">
-        <v>962</v>
+        <v>454</v>
       </c>
       <c r="K4" t="n">
-        <v>1876903</v>
+        <v>704328</v>
       </c>
       <c r="L4" t="n">
-        <v>2644184</v>
+        <v>936253</v>
       </c>
       <c r="M4" t="n">
-        <v>996428</v>
+        <v>344490</v>
       </c>
       <c r="N4" t="n">
-        <v>126577</v>
+        <v>40464</v>
       </c>
       <c r="O4" t="n">
-        <v>424577</v>
+        <v>155543</v>
       </c>
       <c r="P4" t="n">
-        <v>116805</v>
+        <v>44290</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999845027923584</v>
+        <v>0.9999634623527527</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9225093126296997</v>
+        <v>0.8572255373001099</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8434348702430725</v>
+        <v>0.716607391834259</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7777854800224304</v>
+        <v>0.6175291538238525</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5478658080101013</v>
+        <v>0.3497350215911865</v>
       </c>
       <c r="V4" t="n">
-        <v>0.834096372127533</v>
+        <v>0.6950621604919434</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8770455121994019</v>
+        <v>0.7686126828193665</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2585423</v>
+        <v>792041</v>
       </c>
       <c r="Z4" t="n">
-        <v>12547940</v>
+        <v>2160035</v>
       </c>
       <c r="AA4" t="n">
-        <v>847483</v>
+        <v>238897</v>
       </c>
       <c r="AB4" t="n">
-        <v>55399</v>
+        <v>15541</v>
       </c>
       <c r="AC4" t="n">
-        <v>69956</v>
+        <v>29154</v>
       </c>
       <c r="AD4" t="n">
-        <v>7301</v>
+        <v>3538</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2732651</v>
+        <v>839287</v>
       </c>
       <c r="AG4" t="n">
-        <v>3472495</v>
+        <v>1044052</v>
       </c>
       <c r="AH4" t="n">
-        <v>1401491</v>
+        <v>402795</v>
       </c>
       <c r="AI4" t="n">
-        <v>245084</v>
+        <v>62300</v>
       </c>
       <c r="AJ4" t="n">
-        <v>598410</v>
+        <v>181119</v>
       </c>
       <c r="AK4" t="n">
-        <v>170354</v>
+        <v>53568</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8913861513137817</v>
+        <v>0.8336060047149658</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7809774279594421</v>
+        <v>0.6704755425453186</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6961576342582703</v>
+        <v>0.5634252429008484</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.4447703659534454</v>
+        <v>0.2944370806217194</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.763759434223175</v>
+        <v>0.6426298022270203</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.8235925436019897</v>
+        <v>0.7225802540779114</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="D5" t="n">
-        <v>59482</v>
+        <v>22616</v>
       </c>
       <c r="E5" t="n">
-        <v>693496</v>
+        <v>231466</v>
       </c>
       <c r="F5" t="n">
-        <v>3590844</v>
+        <v>569968</v>
       </c>
       <c r="G5" t="n">
-        <v>51661</v>
+        <v>15667</v>
       </c>
       <c r="H5" t="n">
-        <v>233906</v>
+        <v>83321</v>
       </c>
       <c r="I5" t="n">
-        <v>16687</v>
+        <v>8382</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1927674</v>
+        <v>694877</v>
       </c>
       <c r="L5" t="n">
-        <v>2434302</v>
+        <v>907757</v>
       </c>
       <c r="M5" t="n">
-        <v>1055391</v>
+        <v>361537</v>
       </c>
       <c r="N5" t="n">
-        <v>228163</v>
+        <v>61374</v>
       </c>
       <c r="O5" t="n">
-        <v>420466</v>
+        <v>155242</v>
       </c>
       <c r="P5" t="n">
-        <v>120440</v>
+        <v>45035</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999880194664001</v>
+        <v>0.9999717473983765</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9526511430740356</v>
+        <v>0.9129327535629272</v>
       </c>
       <c r="S5" t="n">
-        <v>0.936797022819519</v>
+        <v>0.8852542638778687</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9744645953178406</v>
+        <v>0.9560666084289551</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9955852031707764</v>
+        <v>0.9936630129814148</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9894832372665405</v>
+        <v>0.9806610345840454</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9970474243164062</v>
+        <v>0.9944416284561157</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>92185</v>
+        <v>32315</v>
       </c>
       <c r="Z5" t="n">
-        <v>896478</v>
+        <v>252709</v>
       </c>
       <c r="AA5" t="n">
-        <v>3229049</v>
+        <v>523313</v>
       </c>
       <c r="AB5" t="n">
-        <v>73278</v>
+        <v>17597</v>
       </c>
       <c r="AC5" t="n">
-        <v>327191</v>
+        <v>94225</v>
       </c>
       <c r="AD5" t="n">
-        <v>28054</v>
+        <v>11346</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2617957</v>
+        <v>796876</v>
       </c>
       <c r="AG5" t="n">
-        <v>3565562</v>
+        <v>1079171</v>
       </c>
       <c r="AH5" t="n">
-        <v>1417186</v>
+        <v>408192</v>
       </c>
       <c r="AI5" t="n">
-        <v>246282</v>
+        <v>62682</v>
       </c>
       <c r="AJ5" t="n">
-        <v>602874</v>
+        <v>182502</v>
       </c>
       <c r="AK5" t="n">
-        <v>170624</v>
+        <v>53698</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9334104061126709</v>
+        <v>0.8981877565383911</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9124096632003784</v>
+        <v>0.8678798675537109</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9649208784103394</v>
+        <v>0.9495353698730469</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9938848614692688</v>
+        <v>0.9922228455543518</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9850497245788574</v>
+        <v>0.9773732423782349</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9957564473152161</v>
+        <v>0.9933252334594727</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>370</v>
+        <v>156</v>
       </c>
       <c r="D6" t="n">
-        <v>38584</v>
+        <v>12233</v>
       </c>
       <c r="E6" t="n">
-        <v>55573</v>
+        <v>17040</v>
       </c>
       <c r="F6" t="n">
-        <v>88682</v>
+        <v>18577</v>
       </c>
       <c r="G6" t="n">
-        <v>214925</v>
+        <v>27386</v>
       </c>
       <c r="H6" t="n">
-        <v>40333</v>
+        <v>11628</v>
       </c>
       <c r="I6" t="n">
-        <v>4621</v>
+        <v>1740</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>53118</v>
+        <v>13580</v>
       </c>
       <c r="Z6" t="n">
-        <v>57326</v>
+        <v>16627</v>
       </c>
       <c r="AA6" t="n">
-        <v>79236</v>
+        <v>18486</v>
       </c>
       <c r="AB6" t="n">
-        <v>196806</v>
+        <v>26078</v>
       </c>
       <c r="AC6" t="n">
-        <v>50187</v>
+        <v>11941</v>
       </c>
       <c r="AD6" t="n">
-        <v>6415</v>
+        <v>2048</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>397</v>
+        <v>321</v>
       </c>
       <c r="E7" t="n">
-        <v>40581</v>
+        <v>21902</v>
       </c>
       <c r="F7" t="n">
-        <v>247004</v>
+        <v>89122</v>
       </c>
       <c r="G7" t="n">
-        <v>40854</v>
+        <v>11924</v>
       </c>
       <c r="H7" t="n">
-        <v>2124268</v>
+        <v>354195</v>
       </c>
       <c r="I7" t="n">
-        <v>91553</v>
+        <v>31940</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1680</v>
+        <v>1284</v>
       </c>
       <c r="Z7" t="n">
-        <v>72505</v>
+        <v>31973</v>
       </c>
       <c r="AA7" t="n">
-        <v>347168</v>
+        <v>100506</v>
       </c>
       <c r="AB7" t="n">
-        <v>53385</v>
+        <v>12300</v>
       </c>
       <c r="AC7" t="n">
-        <v>1941860</v>
+        <v>326935</v>
       </c>
       <c r="AD7" t="n">
-        <v>128136</v>
+        <v>36439</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="D8" t="n">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="E8" t="n">
-        <v>2108</v>
+        <v>1148</v>
       </c>
       <c r="F8" t="n">
-        <v>8282</v>
+        <v>4229</v>
       </c>
       <c r="G8" t="n">
-        <v>2457</v>
+        <v>1036</v>
       </c>
       <c r="H8" t="n">
-        <v>107358</v>
+        <v>38546</v>
       </c>
       <c r="I8" t="n">
-        <v>846145</v>
+        <v>148358</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>245</v>
+        <v>67</v>
       </c>
       <c r="Z8" t="n">
-        <v>4228</v>
+        <v>2213</v>
       </c>
       <c r="AA8" t="n">
-        <v>14306</v>
+        <v>6025</v>
       </c>
       <c r="AB8" t="n">
-        <v>4136</v>
+        <v>1511</v>
       </c>
       <c r="AC8" t="n">
-        <v>147709</v>
+        <v>43882</v>
       </c>
       <c r="AD8" t="n">
-        <v>795961</v>
+        <v>139695</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
